--- a/Config/GameConfig/Datas/forniture.xlsx
+++ b/Config/GameConfig/Datas/forniture.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D33DD5E-823E-418E-AB22-18EC12E4EA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3DF1A0-A9A7-4D4B-AA46-D57CB4583836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -57,9 +57,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -166,10 +163,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WHITE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>DESK</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -183,6 +176,10 @@
   </si>
   <si>
     <t>最简陋的凳子</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -604,16 +601,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -661,25 +658,25 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -700,14 +697,14 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -729,25 +726,25 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -771,16 +768,16 @@
         <v>1200001</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="G6">
         <v>30</v>
@@ -791,16 +788,16 @@
         <v>1200002</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="G7">
         <v>15</v>

--- a/Config/GameConfig/Datas/forniture.xlsx
+++ b/Config/GameConfig/Datas/forniture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3DF1A0-A9A7-4D4B-AA46-D57CB4583836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A338EEC-081D-4BA3-8A2E-F6FC71AFDC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -765,7 +765,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6">
-        <v>1200001</v>
+        <v>3000001</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>20</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B7">
-        <v>1200002</v>
+        <v>3000002</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>21</v>
